--- a/generated/spreadsheet/verbose/permission-in-principle-pip-verbose.xlsx
+++ b/generated/spreadsheet/verbose/permission-in-principle-pip-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,75 +1444,75 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,21 +1522,13 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1546,21 +1546,29 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1570,7 +1578,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1604,19 +1612,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1626,7 +1634,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1660,19 +1668,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -1716,19 +1724,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -1772,19 +1780,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1794,7 +1802,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1818,29 +1826,21 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -1888,12 +1888,12 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1903,8 +1903,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1912,55 +1920,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1968,23 +1960,31 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2018,21 +2018,29 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2042,7 +2050,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2076,24 +2084,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2103,72 +2111,64 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2186,21 +2186,29 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2210,7 +2218,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2244,19 +2252,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2266,7 +2274,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2300,19 +2308,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2356,19 +2364,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2412,19 +2420,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2434,53 +2442,45 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2490,21 +2490,13 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2512,23 +2504,31 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2562,21 +2562,29 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2586,7 +2594,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2620,24 +2628,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2647,85 +2655,77 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>phone-numbers</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>conflict-of-interest</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2736,12 +2736,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2751,16 +2751,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2768,12 +2760,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>conflict-person-name</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -2784,17 +2776,17 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2808,12 +2800,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2824,7 +2816,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2839,21 +2831,29 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2864,7 +2864,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2874,21 +2874,13 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2896,12 +2888,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2912,12 +2904,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2936,12 +2928,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2952,12 +2944,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2967,21 +2959,29 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposed development including any non-residential development</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details-inc-non-residential</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of the residential and non-residential parts of the proposed development.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2992,7 +2992,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Description of proposed development including non-residential development</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -3007,16 +3007,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposed development including any non-residential development</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details-inc-non-residential</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Details of the residential and non-residential parts of the proposed development.</t>
@@ -3024,12 +3016,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>net-dwellings-min</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Net dwellings minimum</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3040,12 +3032,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Description of proposed development including non-residential development</t>
+          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3064,12 +3056,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>net-dwellings-min</t>
+          <t>net-dwellings-max</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings minimum</t>
+          <t>Net dwellings maximum</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3080,7 +3072,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
+          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3104,28 +3096,36 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>net-dwellings-max</t>
+          <t>non-residential-use</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings maximum</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+          <t>Non-residential use[]</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>non-residential-measurement-type</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Non-residential measurement type</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
+          <t>Type of measurement being provided (floorspace or site-area)</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>non-residential-measurement-type</t>
+          <t>exact-value</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Non-residential measurement type</t>
+          <t>Exact value</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3168,17 +3168,17 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Type of measurement being provided (floorspace or site-area)</t>
+          <t>Exact figure of non-residential use</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>exact-value</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Exact value</t>
+          <t>Minimum value</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3216,7 +3216,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Exact figure of non-residential use</t>
+          <t>Lower bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Minimum value</t>
+          <t>Maximum value</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Lower bound of non-residential use for ranges</t>
+          <t>Upper bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3279,31 +3279,39 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="n"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential and non-residential parts of the proposed development.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>non-residential-use</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Non-residential use[]</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Maximum value</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3312,12 +3320,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Upper bound of non-residential use for ranges</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3327,16 +3335,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -3354,12 +3354,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3368,12 +3368,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3416,7 +3416,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3464,12 +3464,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -3512,7 +3512,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3560,7 +3560,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3608,7 +3608,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3656,12 +3656,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3704,7 +3704,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3719,31 +3719,39 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Site information</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>site-info</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Any additional relevant information about the development site.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>site-area</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Site area</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>value</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3752,31 +3760,23 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Numeric value representing a measurement or quantity</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Site information</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>site-info</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Any additional relevant information about the development site.</t>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3808,12 +3808,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Numeric value representing a measurement or quantity</t>
+          <t>Unit of measurement for a value</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>provided-by</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3856,17 +3856,17 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Unit of measurement for a value</t>
+          <t>Whether the information was provided by the applicant or calculated by the system</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3880,31 +3880,39 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>site-area</t>
+          <t>existing-use</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Site area</t>
+          <t>Existing use[]</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>provided-by</t>
+          <t>uses</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>Uses[]</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Whether the information was provided by the applicant or calculated by the system</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3914,7 +3922,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3948,29 +3956,29 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>specified-use</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3994,39 +4002,31 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>uses</t>
+          <t>floorspace</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Uses[]</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>specified-use</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Specified use</t>
-        </is>
-      </c>
+          <t>Floorspace</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Total floorspace for a use in square metres</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4040,36 +4040,28 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>existing-use</t>
+          <t>known-constraints</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Existing use[]</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>floorspace</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Floorspace</t>
-        </is>
-      </c>
+          <t>Known constraints[]</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Total floorspace for a use in square metres</t>
+          <t>A list of the known constraints affecting the site</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -4088,28 +4080,36 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>known-constraints</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Known constraints[]</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>A list of the known constraints affecting the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>details</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4152,7 +4152,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Additional details or information about an item</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4161,54 +4161,6 @@
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Any additional relevant information about the development site.</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>supporting-documents</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>details</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>Additional details or information about an item</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -4216,28 +4168,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B32:B37"/>
-    <mergeCell ref="A65:A73"/>
-    <mergeCell ref="B20:B27"/>
-    <mergeCell ref="A56:A64"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B65:B73"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="B56:B64"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A20:A27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A42"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="B48:B54"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="A55:A63"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B41"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B64:B72"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="A64:A72"/>
+    <mergeCell ref="B19:B26"/>
+    <mergeCell ref="A41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A19:A26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/permission-in-principle-pip-verbose.xlsx
+++ b/generated/spreadsheet/verbose/permission-in-principle-pip-verbose.xlsx
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/permission-in-principle-pip-verbose.xlsx
+++ b/generated/spreadsheet/verbose/permission-in-principle-pip-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -521,37 +521,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>submission-reference</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,27 +627,27 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>specification-profile</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -675,27 +675,27 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -723,27 +723,27 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>submitted-at</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -771,49 +771,41 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>created-at</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -827,17 +819,17 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -852,19 +844,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -883,17 +875,17 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -908,19 +900,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -930,7 +922,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -939,17 +931,17 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -964,29 +956,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -995,17 +987,17 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1020,24 +1012,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1051,17 +1043,17 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1076,37 +1068,29 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>base64-content</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1099,17 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,17 +1134,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>base64-content</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1163,17 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,17 +1198,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1234,7 +1218,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>file-size</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1307,54 +1291,62 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>file-size</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1355,17 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1388,24 +1380,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1419,17 +1411,17 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1444,75 +1436,75 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1522,13 +1514,21 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1546,29 +1546,21 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1578,7 +1570,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1612,19 +1604,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1634,7 +1626,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1668,19 +1660,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -1724,19 +1716,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -1780,19 +1772,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1802,7 +1794,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1826,21 +1818,29 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -1888,12 +1888,12 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1903,16 +1903,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1920,39 +1912,55 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1960,31 +1968,23 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2018,29 +2018,21 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2050,7 +2042,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2084,24 +2076,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,64 +2103,72 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2186,29 +2186,21 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2218,7 +2210,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2252,19 +2244,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2274,7 +2266,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2308,19 +2300,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2364,19 +2356,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2420,19 +2412,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2442,45 +2434,53 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2490,13 +2490,21 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2504,31 +2512,23 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2562,29 +2562,21 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2594,7 +2586,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2628,24 +2620,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2655,77 +2647,85 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>phone-numbers</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2736,12 +2736,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2751,8 +2751,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2760,12 +2768,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -2776,17 +2784,17 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2800,12 +2808,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2816,7 +2824,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2831,29 +2839,21 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2864,7 +2864,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2874,13 +2874,21 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2888,12 +2896,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2904,12 +2912,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2928,12 +2936,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2944,12 +2952,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2959,29 +2967,21 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposed development including any non-residential development</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details-inc-non-residential</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential and non-residential parts of the proposed development.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2992,12 +2992,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Description of proposed development including non-residential development</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3007,8 +3007,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposed development including any non-residential development</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details-inc-non-residential</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Details of the residential and non-residential parts of the proposed development.</t>
@@ -3016,12 +3024,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>net-dwellings-min</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings minimum</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3032,12 +3040,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
+          <t>Description of proposed development including non-residential development</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3056,12 +3064,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>net-dwellings-max</t>
+          <t>net-dwellings-min</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings maximum</t>
+          <t>Net dwellings minimum</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3072,12 +3080,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
+          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3096,36 +3104,28 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>non-residential-use</t>
+          <t>net-dwellings-max</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Non-residential use[]</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>non-residential-measurement-type</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Non-residential measurement type</t>
-        </is>
-      </c>
+          <t>Net dwellings maximum</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Type of measurement being provided (floorspace or site-area)</t>
+          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>exact-value</t>
+          <t>non-residential-measurement-type</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Exact value</t>
+          <t>Non-residential measurement type</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3168,17 +3168,17 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Exact figure of non-residential use</t>
+          <t>Type of measurement being provided (floorspace or site-area)</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>exact-value</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Minimum value</t>
+          <t>Exact value</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Lower bound of non-residential use for ranges</t>
+          <t>Exact figure of non-residential use</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Maximum value</t>
+          <t>Minimum value</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3264,12 +3264,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Upper bound of non-residential use for ranges</t>
+          <t>Lower bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3279,39 +3279,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of the residential and non-residential parts of the proposed development.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>non-residential-use</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Non-residential use[]</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Maximum value</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3320,12 +3312,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Upper bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3335,8 +3327,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -3354,12 +3354,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3368,12 +3368,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3416,7 +3416,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3464,12 +3464,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -3512,12 +3512,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3560,12 +3560,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3608,12 +3608,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3656,12 +3656,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3704,7 +3704,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3719,39 +3719,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Site information</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>site-info</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Any additional relevant information about the development site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>site-area</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Site area</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3760,23 +3752,31 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Numeric value representing a measurement or quantity</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Site information</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>site-info</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Any additional relevant information about the development site.</t>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>size</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3808,12 +3808,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Unit of measurement for a value</t>
+          <t>Size of the development site area</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>provided-by</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3856,17 +3856,17 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Whether the information was provided by the applicant or calculated by the system</t>
+          <t>Unit of measurement for a value</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3880,39 +3880,31 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>existing-use</t>
+          <t>site-area</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Existing use[]</t>
+          <t>Site area</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>uses</t>
+          <t>provided-by</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Uses[]</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Provided by</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Whether the information was provided by the applicant or calculated by the system</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3922,7 +3914,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3956,29 +3948,29 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>specified-use</t>
+          <t>use</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4002,31 +3994,39 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>floorspace</t>
+          <t>uses</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Floorspace</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
+          <t>Uses[]</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>specified-use</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Specified use</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Total floorspace for a use in square metres</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4040,28 +4040,36 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>known-constraints</t>
+          <t>existing-use</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Known constraints[]</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+          <t>Existing use[]</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>floorspace</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Floorspace</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>A list of the known constraints affecting the site</t>
+          <t>Total floorspace for a use in square metres</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -4080,36 +4088,28 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>known-constraints</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Known constraints[]</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A list of the known constraints affecting the site</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>details</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4152,15 +4152,63 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Any additional relevant information about the development site.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
           <t>Additional details or information about an item</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -4168,28 +4216,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="B48:B54"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="A55:A63"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="B41"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B64:B72"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="A64:A72"/>
-    <mergeCell ref="B19:B26"/>
-    <mergeCell ref="A41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A19:A26"/>
+    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="A65:A73"/>
+    <mergeCell ref="B20:B27"/>
+    <mergeCell ref="A56:A64"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="B49:B55"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B65:B73"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B42"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="A32:A37"/>
+    <mergeCell ref="B56:B64"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A20:A27"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/permission-in-principle-pip-verbose.xlsx
+++ b/generated/spreadsheet/verbose/permission-in-principle-pip-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -440,9 +440,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1772,19 +1772,27 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1828,19 +1836,27 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1874,21 +1890,37 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1922,12 +1954,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -1936,12 +1968,12 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -1951,16 +1983,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1968,28 +1992,36 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1999,8 +2031,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2008,31 +2048,23 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2042,7 +2074,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2066,29 +2098,21 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2098,7 +2122,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2132,24 +2156,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2159,64 +2183,72 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2234,29 +2266,21 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2266,7 +2290,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2300,19 +2324,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2322,7 +2346,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2356,19 +2380,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2412,19 +2436,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2468,77 +2492,101 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>applicant-reference</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2547,92 +2595,100 @@
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
           <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>contact-details</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>phone-numbers</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2642,7 +2698,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2666,77 +2722,77 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>phone-numbers</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -2746,74 +2802,90 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>phone-numbers</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2824,7 +2896,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2834,13 +2906,21 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2848,12 +2928,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2864,34 +2944,26 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2912,7 +2984,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -2922,7 +2994,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2931,17 +3003,17 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2952,23 +3024,31 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2976,12 +3056,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2992,12 +3072,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3007,29 +3087,21 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposed development including any non-residential development</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details-inc-non-residential</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential and non-residential parts of the proposed development.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3040,12 +3112,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Description of proposed development including non-residential development</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3059,17 +3131,17 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential and non-residential parts of the proposed development.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>net-dwellings-min</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings minimum</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3080,12 +3152,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3095,8 +3167,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposed development including any non-residential development</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details-inc-non-residential</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Details of the residential and non-residential parts of the proposed development.</t>
@@ -3104,12 +3184,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>net-dwellings-max</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Net dwellings maximum</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3120,12 +3200,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
+          <t>Description of proposed development including non-residential development</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3144,36 +3224,28 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>non-residential-use</t>
+          <t>net-dwellings-min</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Non-residential use[]</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>non-residential-measurement-type</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Non-residential measurement type</t>
-        </is>
-      </c>
+          <t>Net dwellings minimum</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Type of measurement being provided (floorspace or site-area)</t>
+          <t>The minimum number of net additional dwellings proposed as part of the development, accounting for any existing dwellings lost and new dwellings created</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3192,41 +3264,33 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>non-residential-use</t>
+          <t>net-dwellings-max</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Non-residential use[]</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>exact-value</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Exact value</t>
-        </is>
-      </c>
+          <t>Net dwellings maximum</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Exact figure of non-residential use</t>
+          <t>The maximum number of net additional dwellings proposed as part of the development, allowing for flexibility in the final housing numbers</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3250,12 +3314,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>non-residential-measurement-type</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Minimum value</t>
+          <t>Non-residential measurement type</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3264,17 +3328,17 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Lower bound of non-residential use for ranges</t>
+          <t>Type of measurement being provided (floorspace or site-area)</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3298,12 +3362,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>exact-value</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Maximum value</t>
+          <t>Exact value</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3312,7 +3376,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Upper bound of non-residential use for ranges</t>
+          <t>Exact figure of non-residential use</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3327,39 +3391,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of the residential and non-residential parts of the proposed development.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>non-residential-use</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Non-residential use[]</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>min</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Minimum value</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3368,12 +3424,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Lower bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3387,27 +3443,27 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of the residential and non-residential parts of the proposed development.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>non-residential-use</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Non-residential use[]</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>max</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Maximum value</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3416,12 +3472,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Upper bound of non-residential use for ranges</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -3431,8 +3487,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -3450,12 +3514,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3464,17 +3528,17 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3498,31 +3562,39 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3546,26 +3618,34 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3594,26 +3674,34 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3642,26 +3730,34 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3690,12 +3786,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3704,12 +3800,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3738,12 +3834,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3752,12 +3848,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3767,39 +3863,31 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Site information</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>site-info</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Any additional relevant information about the development site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>site-area</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Site area</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3808,17 +3896,17 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Size of the development site area</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3827,27 +3915,27 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Any additional relevant information about the development site.</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>site-area</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Site area</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3856,23 +3944,31 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Unit of measurement for a value</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Site information</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>site-info</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Any additional relevant information about the development site.</t>
@@ -3890,12 +3986,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>provided-by</t>
+          <t>size</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3904,17 +4000,17 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Whether the information was provided by the applicant or calculated by the system</t>
+          <t>Size of the development site area</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3928,44 +4024,36 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>existing-use</t>
+          <t>site-area</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Existing use[]</t>
+          <t>Site area</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>uses</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Uses[]</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Unit of measurement for a value</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -3984,44 +4072,36 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>existing-use</t>
+          <t>site-area</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Existing use[]</t>
+          <t>Site area</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>uses</t>
+          <t>provided-by</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Uses[]</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>specified-use</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Specified use</t>
-        </is>
-      </c>
+          <t>Provided by</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Whether the information was provided by the applicant or calculated by the system</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4050,26 +4130,34 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>floorspace</t>
+          <t>uses</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Floorspace</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>Uses[]</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Total floorspace for a use in square metres</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -4088,33 +4176,49 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>known-constraints</t>
+          <t>existing-use</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Known constraints[]</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
+          <t>Existing use[]</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>uses</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Uses[]</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>specified-use</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Specified use</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>A list of the known constraints affecting the site</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4128,22 +4232,22 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>existing-use</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Existing use[]</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>floorspace</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Floorspace</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4152,12 +4256,12 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Total floorspace for a use in square metres</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4176,39 +4280,127 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>known-constraints</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>details</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
+          <t>Known constraints[]</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
+          <t>A list of the known constraints affecting the site</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Any additional relevant information about the development site.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Any additional relevant information about the development site.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
           <t>Additional details or information about an item</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -4216,28 +4408,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B32:B37"/>
-    <mergeCell ref="A65:A73"/>
-    <mergeCell ref="B20:B27"/>
-    <mergeCell ref="A56:A64"/>
+    <mergeCell ref="B67:B75"/>
+    <mergeCell ref="B58:B66"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B65:B73"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="B56:B64"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A20:A27"/>
-    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A33:A39"/>
+    <mergeCell ref="B33:B39"/>
+    <mergeCell ref="A20:A28"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B51:B57"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B20:B28"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A58:A66"/>
+    <mergeCell ref="A67:A75"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B44"/>
+    <mergeCell ref="A51:A57"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A42"/>
+    <mergeCell ref="A40:A43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
